--- a/data/trans_orig/IP07A07-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A07-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2007 (tasa de respuesta: 99,6%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal, percibida por el adulto en 2007 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>5254</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>7323</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4637</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14094</t>
+          <t>14194</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17034</t>
+          <t>17714</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>13825</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28395</t>
+          <t>27172</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24344</t>
+          <t>24741</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40218</t>
+          <t>41125</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23833</t>
+          <t>24200</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39999</t>
+          <t>40379</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53356</t>
+          <t>53319</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74648</t>
+          <t>75225</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75794</t>
+          <t>74586</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93049</t>
+          <t>92371</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>87423</t>
+          <t>88211</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>105496</t>
+          <t>105812</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>169293</t>
+          <t>169149</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>194794</t>
+          <t>192549</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>71,56%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>729</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>6932</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>7376</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>721</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6457</t>
+          <t>6556</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5452</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>9936</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23527</t>
+          <t>23663</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39684</t>
+          <t>41359</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14907</t>
+          <t>14871</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29345</t>
+          <t>29642</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42647</t>
+          <t>41634</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>63388</t>
+          <t>64161</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39078</t>
+          <t>36240</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58669</t>
+          <t>57279</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37805</t>
+          <t>37280</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57748</t>
+          <t>57617</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81799</t>
+          <t>82084</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109022</t>
+          <t>109533</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,55%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98360</t>
+          <t>97422</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>120152</t>
+          <t>119056</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>121005</t>
+          <t>121740</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>143306</t>
+          <t>143771</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>226184</t>
+          <t>225302</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>257956</t>
+          <t>255397</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,24%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7747</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8295</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>8904</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8079</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14078</t>
+          <t>13679</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31356</t>
+          <t>31391</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50592</t>
+          <t>50509</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24197</t>
+          <t>24780</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41851</t>
+          <t>42071</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>60151</t>
+          <t>60137</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>86350</t>
+          <t>84989</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>67067</t>
+          <t>68287</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>92559</t>
+          <t>94185</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66679</t>
+          <t>66336</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91880</t>
+          <t>91605</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>141591</t>
+          <t>139856</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>175819</t>
+          <t>175983</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>178312</t>
+          <t>178514</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>207167</t>
+          <t>207503</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>216336</t>
+          <t>216933</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>244543</t>
+          <t>244985</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>403622</t>
+          <t>403206</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>444268</t>
+          <t>444202</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,64%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2012 (tasa de respuesta: 98,23%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal, percibida por el adulto en 2012 (tasa de respuesta: 98,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>736</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8512</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9091</t>
+          <t>9133</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6586</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17642</t>
+          <t>17799</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15834</t>
+          <t>14952</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31122</t>
+          <t>29398</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24857</t>
+          <t>25297</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42872</t>
+          <t>43522</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32354</t>
+          <t>31543</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50401</t>
+          <t>49851</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20243</t>
+          <t>19807</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35746</t>
+          <t>35145</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54956</t>
+          <t>55987</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79974</t>
+          <t>81354</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>26,06%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87554</t>
+          <t>87436</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>106964</t>
+          <t>107648</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>94937</t>
+          <t>95038</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>114014</t>
+          <t>114961</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>189628</t>
+          <t>189508</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>217142</t>
+          <t>218071</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,85%</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>628</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>6661</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>928</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7877</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10350</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12921</t>
+          <t>12409</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17440</t>
+          <t>18038</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32836</t>
+          <t>33280</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22608</t>
+          <t>22314</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38330</t>
+          <t>38408</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>43486</t>
+          <t>43890</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>66423</t>
+          <t>66020</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37923</t>
+          <t>37307</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56851</t>
+          <t>56731</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34989</t>
+          <t>34579</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52837</t>
+          <t>52955</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>77289</t>
+          <t>77723</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103707</t>
+          <t>103998</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,32%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>79245</t>
+          <t>78420</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>99078</t>
+          <t>99387</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>88035</t>
+          <t>87497</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>109063</t>
+          <t>108713</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>172899</t>
+          <t>173767</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>203911</t>
+          <t>202558</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,06%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8475</t>
+          <t>8525</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8221</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13493</t>
+          <t>13563</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>4769</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14043</t>
+          <t>15126</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6088</t>
+          <t>6784</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7044</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17789</t>
+          <t>17253</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26577</t>
+          <t>27529</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>44839</t>
+          <t>47054</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>42256</t>
+          <t>42182</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63259</t>
+          <t>63601</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>73368</t>
+          <t>75284</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>103061</t>
+          <t>103683</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74190</t>
+          <t>73687</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>100394</t>
+          <t>100982</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59820</t>
+          <t>59224</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>83302</t>
+          <t>82641</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>139701</t>
+          <t>140364</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>175810</t>
+          <t>177557</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>172597</t>
+          <t>172707</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>202895</t>
+          <t>202068</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>188719</t>
+          <t>189451</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>216150</t>
+          <t>217487</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>370177</t>
+          <t>369716</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>411319</t>
+          <t>409532</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,51%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2016 (tasa de respuesta: 98,92%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal, percibida por el adulto en 2016 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7666</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1427</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>8391</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14862</t>
+          <t>14855</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>4554</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14670</t>
+          <t>14294</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11715</t>
+          <t>12607</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25723</t>
+          <t>26634</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8736</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20612</t>
+          <t>21006</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,47 +5525,47 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>4,87%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>11,29%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>14204</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>8812</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>21017</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>7,58%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
           <t>4,7%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,08%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>14204</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>8958</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>21719</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>7,58%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20633</t>
+          <t>20887</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37639</t>
+          <t>37232</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30370</t>
+          <t>30169</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48570</t>
+          <t>48263</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30748</t>
+          <t>30819</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48906</t>
+          <t>48818</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65737</t>
+          <t>65106</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91108</t>
+          <t>91155</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,42%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>112805</t>
+          <t>112885</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>133799</t>
+          <t>133757</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>111076</t>
+          <t>111979</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>132435</t>
+          <t>133295</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>230089</t>
+          <t>228223</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>259331</t>
+          <t>259450</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>69,5%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6392</t>
+          <t>7251</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9141</t>
+          <t>9482</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>3917</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13386</t>
+          <t>12961</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7146</t>
+          <t>7145</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18609</t>
+          <t>18837</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2685</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11472</t>
+          <t>10940</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11616</t>
+          <t>12235</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26538</t>
+          <t>26847</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13642</t>
+          <t>13659</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27089</t>
+          <t>27005</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6933</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18315</t>
+          <t>18467</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22449</t>
+          <t>24089</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39643</t>
+          <t>40592</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6305,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31283</t>
+          <t>30510</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49846</t>
+          <t>48930</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34210</t>
+          <t>33934</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53000</t>
+          <t>53329</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70540</t>
+          <t>69786</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95128</t>
+          <t>96704</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,1%</t>
         </is>
       </c>
     </row>
@@ -6418,12 +6418,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85615</t>
+          <t>85838</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>106576</t>
+          <t>107824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>96422</t>
+          <t>96390</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>118008</t>
+          <t>117652</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>190467</t>
+          <t>188504</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>219800</t>
+          <t>218918</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,62%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7136</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14159</t>
+          <t>13590</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6827</t>
+          <t>7025</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17723</t>
+          <t>17957</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15063</t>
+          <t>14960</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29546</t>
+          <t>29316</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8861</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22520</t>
+          <t>21689</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27538</t>
+          <t>27335</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46346</t>
+          <t>46486</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25483</t>
+          <t>25517</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43129</t>
+          <t>44103</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18394</t>
+          <t>17777</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34606</t>
+          <t>34998</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>47603</t>
+          <t>47373</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>72935</t>
+          <t>72539</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65392</t>
+          <t>66085</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>91741</t>
+          <t>91831</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>71115</t>
+          <t>69426</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>95342</t>
+          <t>95045</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>142948</t>
+          <t>144112</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>179003</t>
+          <t>181989</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -7100,12 +7100,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>205625</t>
+          <t>205433</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>235299</t>
+          <t>234217</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>214060</t>
+          <t>214285</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>243656</t>
+          <t>244691</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7150,12 +7150,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>429540</t>
+          <t>427074</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>471547</t>
+          <t>472398</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,85%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07A07-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A07-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentir que todo le sale mal, percibida por el adulto en 2007 (tasa de respuesta: 99,6%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal, percibida por el/la adulto/a [KIDSCREEN 20] en 2007 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>654</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3793</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3309</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,51%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3961</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3307</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1378</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4911</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>1945</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>629</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5254</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5209</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,49%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1378</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>4206</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7323</t>
+          <t>7611</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11384</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6896</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17645</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4,87%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>12,47%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>8515</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5107</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>14194</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>4731</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>13747</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>6,68%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,13%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>11384</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>6645</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>17714</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>8,04%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13825</t>
+          <t>13762</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27172</t>
+          <t>27555</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>31846</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>24996</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>41237</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>22,5%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>17,66%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>29,14%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>31907</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>24741</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>41125</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>24291</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>39600</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>25,02%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>19,4%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>32,24%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>31846</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>24200</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>40379</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>22,5%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53319</t>
+          <t>52538</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75225</t>
+          <t>75224</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1174,72 +1174,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>96907</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>87174</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>105337</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>68,48%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>61,6%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>74,44%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>84527</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>74586</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>92371</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>76344</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>92721</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>66,27%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>58,48%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>72,42%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>96907</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>88211</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>105812</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>68,48%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>169149</t>
+          <t>167550</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>192549</t>
+          <t>193524</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,93%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,74 +1404,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3085</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2815</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>729</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>6932</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,45%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>3,58%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3353</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>5</t>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>7046</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>2805</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>721</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6556</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>728</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>6915</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>1,45%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>5436</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9936</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>21175</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15173</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>29223</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>10,38%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>7,44%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>14,32%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>31347</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>23663</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>41359</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>24444</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>39604</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>16,2%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>12,23%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>21,38%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>21175</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>14871</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>29642</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>10,38%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>41634</t>
+          <t>41743</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>64161</t>
+          <t>62881</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -1748,67 +1748,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>47053</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>37670</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>57159</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>23,06%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>18,46%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>28,01%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>47647</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>36240</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>57279</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>38847</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>57456</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>24,63%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>18,73%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>29,61%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>47053</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>37280</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>57617</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>23,06%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82084</t>
+          <t>81668</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109533</t>
+          <t>107614</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,07%</t>
         </is>
       </c>
     </row>
@@ -1856,72 +1856,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>133205</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>122564</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>143858</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>65,27%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>60,06%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>70,49%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>108851</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>97422</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>119056</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>97020</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>119281</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>56,26%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>50,36%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>61,54%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>133205</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>121740</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>143771</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>65,27%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>225302</t>
+          <t>227332</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>255397</t>
+          <t>259076</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>65,17%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>193465</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>193465</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>193465</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3086</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>3469</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1292</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7747</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7775</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,08%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3059</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8378</t>
+          <t>8362</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3403</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>7523</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>4749</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1920</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8904</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2069</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>10742</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>1,48%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3403</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1345</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>7480</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13679</t>
+          <t>13747</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>32558</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>24172</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>41874</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>9,42%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>6,99%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>12,12%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>39862</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>31391</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>50509</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>31284</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>50825</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>12,42%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>9,78%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>15,73%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>32558</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>24780</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>42071</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>9,42%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>60137</t>
+          <t>60950</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>84989</t>
+          <t>86009</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>78900</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>66266</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>91858</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>22,83%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>19,17%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>26,58%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>79554</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>68287</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>94185</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>66866</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>92157</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>24,78%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>21,27%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>29,34%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>78900</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>66336</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>91605</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>22,83%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>139856</t>
+          <t>140389</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>175983</t>
+          <t>176121</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,42%</t>
         </is>
       </c>
     </row>
@@ -2538,72 +2538,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>230112</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>216014</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>243985</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>66,59%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>62,51%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>70,6%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>193378</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>178514</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>207503</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>179784</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>208899</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>60,24%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>55,61%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>64,64%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>230112</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>216933</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>244985</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>66,59%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>403206</t>
+          <t>403974</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>444202</t>
+          <t>444534</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,69%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>476</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>321012</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>321012</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>321012</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentir que todo le sale mal, percibida por el adulto en 2012 (tasa de respuesta: 98,23%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal, percibida por el/la adulto/a [KIDSCREEN 20] en 2012 (tasa de respuesta: 98,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1358</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4703</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2823</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>736</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7068</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7716</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,82%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1358</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4747</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1451</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5127</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>3187</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1231</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7119</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7100</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>2,05%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1451</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>4516</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9133</t>
+          <t>8860</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>22157</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15913</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>31149</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>14,14%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>10,16%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>19,88%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>11182</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6654</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>17799</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>6643</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>17185</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>7,19%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,45%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>22157</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>14952</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>29398</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>14,14%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25297</t>
+          <t>24780</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43522</t>
+          <t>43571</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -3337,72 +3337,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>26767</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>20208</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>35268</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17,08%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12,9%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>22,51%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>40313</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>31543</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>49851</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>30905</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>49650</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>25,92%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>20,28%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>32,06%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>26767</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>19807</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>35145</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>17,08%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>55987</t>
+          <t>54732</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81354</t>
+          <t>78315</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -3450,72 +3450,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>104942</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>95139</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>114757</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>66,98%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>60,72%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>73,25%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>98009</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>87436</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>107648</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>88096</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>108638</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>63,02%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>56,22%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>69,22%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>104942</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>95038</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>114961</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>66,98%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>189508</t>
+          <t>188519</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>218071</t>
+          <t>217419</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,64%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2320</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5882</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1312</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4595</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3986</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,79%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2320</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6661</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>7814</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1205</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4195</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>5410</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2577</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>10180</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2134</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>10074</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>3,24%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>6,09%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1205</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>4212</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3465</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12409</t>
+          <t>11750</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>30070</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>22706</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>38951</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>17,1%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>12,91%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>22,15%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>24706</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>18038</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>33280</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>18498</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>33492</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>14,78%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>10,79%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>19,91%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>30070</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>22314</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>38408</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>17,1%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>43890</t>
+          <t>44489</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>66020</t>
+          <t>66715</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>43865</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>34829</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>52670</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>24,95%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>19,81%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>29,95%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>46659</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>37307</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>56731</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>37636</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>56760</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>27,92%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>22,32%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>33,94%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>43865</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>34579</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>52955</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>24,95%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>77723</t>
+          <t>78971</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103998</t>
+          <t>104883</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,58%</t>
         </is>
       </c>
     </row>
@@ -4132,72 +4132,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>98374</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>87128</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>108960</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>55,95%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>49,55%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>61,97%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>89043</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>78420</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>99387</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>78368</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>99683</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>53,28%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>46,92%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>59,47%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>98374</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>87497</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>108713</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>55,95%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>173767</t>
+          <t>172753</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>202558</t>
+          <t>202491</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>59,04%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>175834</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>175834</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>175834</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>167130</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>167130</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>167130</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>175834</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>175834</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>175834</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3677</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1212</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8792</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>4136</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1465</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8525</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1437</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8577</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,28%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3677</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1362</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>8221</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13563</t>
+          <t>13675</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2656</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>773</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>6778</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>8597</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>4769</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>15126</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>4632</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>14327</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>2,66%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>2656</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>6784</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>6649</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17253</t>
+          <t>17631</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>52227</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>41627</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>63768</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>15,71%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>12,52%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>19,18%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>35888</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>27529</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>47054</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>28442</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>46259</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>11,12%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>8,53%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>14,58%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>52227</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>42182</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>63601</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>15,71%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>75284</t>
+          <t>73687</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>103683</t>
+          <t>103224</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -4701,107 +4701,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>70633</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>59289</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>83075</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>21,24%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>17,83%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>24,98%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>86972</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>73687</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>100982</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>73869</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>100553</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>26,96%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>22,84%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>31,3%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>70633</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>59224</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>82641</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>22,89%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>31,17%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>157605</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>139125</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>176235</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>24,06%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>21,24%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>17,81%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>24,85%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>157605</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>140364</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>177557</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>24,06%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>21,42%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,9%</t>
         </is>
       </c>
     </row>
@@ -4814,72 +4814,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>203315</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>188635</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>217666</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>61,15%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>56,73%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>65,46%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>187052</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>172707</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>202068</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>172111</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>200318</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>57,97%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>53,53%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>62,63%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>203315</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>189451</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>217487</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>61,15%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>369716</t>
+          <t>369155</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>409532</t>
+          <t>411597</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,82%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>332508</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>332508</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>332508</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>458</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>322645</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>322645</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>322645</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>332508</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>332508</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>332508</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentir que todo le sale mal, percibida por el adulto en 2016 (tasa de respuesta: 98,92%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal, percibida por el/la adulto/a [KIDSCREEN 20] en 2016 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1383</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8091</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,32%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>524</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2635</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2660</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3500</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1371</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7767</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8391</t>
+          <t>8705</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8719</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4756</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14415</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4,65%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>9369</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5085</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14855</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5507</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>15565</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>5,04%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7,99%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8719</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>4554</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>14294</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12607</t>
+          <t>11961</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26634</t>
+          <t>26074</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -5505,67 +5505,67 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>14204</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9414</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21740</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,58%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5,03%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>11,61%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>13984</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9056</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>21006</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>9076</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>20845</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>7,52%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,87%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,29%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>14204</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>8812</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>21017</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>7,58%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20887</t>
+          <t>20552</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37232</t>
+          <t>37252</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -5618,67 +5618,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>39088</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>30387</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>48188</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>20,87%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>16,22%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>25,73%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>38665</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>30169</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>48263</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>30239</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>48787</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>20,79%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16,22%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>25,95%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>39088</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>30819</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>48818</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>20,87%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65106</t>
+          <t>64236</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91155</t>
+          <t>90421</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -5726,72 +5726,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>121802</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>111354</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>132955</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>65,03%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>59,45%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>70,98%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>123441</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>112885</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>133757</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>112200</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>134581</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>66,37%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>60,7%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>71,92%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>121802</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>111979</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>133295</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>65,03%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>228223</t>
+          <t>230498</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>259450</t>
+          <t>261137</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,95%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>187313</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>187313</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>187313</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>267</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>187313</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>187313</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>187313</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4813</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9282</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,36%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2988</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1137</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7251</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1173</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6522</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,75%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2036</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9482</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>13001</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -6069,107 +6069,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6015</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2840</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>11654</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>6,72%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>12140</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>7145</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>18837</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>7495</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>18435</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>7,11%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>11,03%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>6015</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2733</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>10940</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>4,39%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>10,79%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>18155</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>11945</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>26063</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>5,28%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>3,47%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>6,31%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>18155</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>12235</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>26847</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>5,28%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11723</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7074</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18427</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6,76%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10,63%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>19408</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>13659</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>27005</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>12982</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>26888</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>11,36%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>8,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>15,81%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>11723</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>7155</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>18467</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>6,76%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24089</t>
+          <t>23034</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40592</t>
+          <t>40598</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -6295,72 +6295,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>43060</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>34377</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>53437</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>24,84%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>19,83%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>30,83%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>39752</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>30510</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>48930</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>31871</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>50500</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>23,28%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17,86%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>28,65%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>43060</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>33934</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>53329</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>24,84%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69786</t>
+          <t>70139</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96704</t>
+          <t>97427</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,31%</t>
         </is>
       </c>
     </row>
@@ -6408,72 +6408,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>107710</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>96588</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>118121</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>62,14%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>55,73%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>68,15%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>96501</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>85838</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>107824</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>86309</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>107028</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>56,5%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>50,26%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>63,13%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>107710</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>96390</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>117652</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>62,14%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>188504</t>
+          <t>186528</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>218918</t>
+          <t>217637</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,25%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173322</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173322</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173322</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>170789</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>170789</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>170789</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173322</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173322</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173322</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8313</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4838</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>14623</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,05%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>3512</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1302</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7397</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1291</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7041</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,98%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>8313</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>4646</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>13590</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7025</t>
+          <t>7354</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17957</t>
+          <t>18476</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>14734</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9631</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>22430</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>21509</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>14960</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>29316</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>14422</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>29643</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>6,03%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>4,19%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>8,22%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>14734</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>9044</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>21689</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27335</t>
+          <t>27187</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46486</t>
+          <t>47677</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -6864,72 +6864,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>25927</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>18905</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>34799</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>7,19%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>9,65%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>33392</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>25517</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>44103</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>24781</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>43410</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>9,36%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>7,15%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>12,36%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>25927</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>17777</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>34998</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>7,19%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>47373</t>
+          <t>48316</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>72539</t>
+          <t>74084</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>82149</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>69532</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>96427</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>22,78%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>19,28%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>26,74%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>78417</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>66085</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>91831</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>66484</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>92190</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>21,98%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>18,52%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>25,74%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>82149</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>69426</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>95045</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>22,78%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>144112</t>
+          <t>143174</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>181989</t>
+          <t>180165</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -7095,67 +7095,67 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>229513</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>213116</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>244093</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>63,64%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>59,09%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>67,68%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>219942</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>205433</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>234217</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>204536</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>234608</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>61,65%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>57,58%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>65,65%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>229513</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>214285</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>244691</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>63,64%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>427074</t>
+          <t>428330</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>472398</t>
+          <t>472412</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,7 +7185,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>360636</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>360636</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>360636</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>510</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>356772</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>356772</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>356772</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>360636</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>360636</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>360636</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
